--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdStandardBond001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdStandardBond001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yitihua_idea\pingan-parent\pingan-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tamsideaworkspace\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20385" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20390" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,8 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-m\-d"/>
+  <numFmts count="1">
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -105,11 +104,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -416,42 +413,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="15.625" customWidth="1"/>
-    <col min="5" max="7" width="15.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="9" customWidth="1"/>
+    <col min="1" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="7" width="15.6328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
